--- a/data/trans_orig/P33_MIN_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nº medio de minutos durante los cuales la población se echa la siesta</t>
+          <t>Nº medio de minutos durante los cuales la población se echa la siesta (tasa de respuesta: 37,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 63,09</t>
+          <t>32,17; 65,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,53; 83,96</t>
+          <t>48,48; 83,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,48; 67,15</t>
+          <t>44,96; 67,91</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,97; 52,82</t>
+          <t>33,03; 53,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,0; 76,65</t>
+          <t>39,93; 75,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,78; 57,17</t>
+          <t>38,96; 58,19</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 40,27</t>
+          <t>27,01; 39,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,88; 37,38</t>
+          <t>25,8; 37,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 36,78</t>
+          <t>28,12; 37,07</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 42,05</t>
+          <t>6,58; 42,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,76; 39,88</t>
+          <t>30,81; 40,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 39,25</t>
+          <t>8,47; 39,03</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,55; 39,22</t>
+          <t>30,36; 38,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,26; 35,59</t>
+          <t>26,85; 35,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 36,41</t>
+          <t>30,05; 36,2</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,24; 43,72</t>
+          <t>33,87; 43,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 34,46</t>
+          <t>4,21; 34,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 36,92</t>
+          <t>6,76; 36,86</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,75; 45,46</t>
+          <t>35,49; 46,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,8; 41,38</t>
+          <t>32,93; 41,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,42; 41,55</t>
+          <t>35,4; 41,71</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,8; 39,11</t>
+          <t>18,75; 39,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 38,22</t>
+          <t>17,58; 38,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,82; 37,62</t>
+          <t>23,07; 38,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_MIN_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,45</t>
+          <t>43,48</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>64,83</t>
+          <t>62,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55,56</t>
+          <t>53,14</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 65,07</t>
+          <t>30,05; 58,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,48; 83,95</t>
+          <t>46,92; 78,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,96; 67,91</t>
+          <t>42,69; 64,57</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41,88</t>
+          <t>42,68</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50,67</t>
+          <t>48,14</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,2</t>
+          <t>45,36</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 53,19</t>
+          <t>33,54; 53,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,93; 75,44</t>
+          <t>38,71; 70,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,96; 58,19</t>
+          <t>37,95; 55,26</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33,17</t>
+          <t>33,98</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,87</t>
+          <t>31,98</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,18</t>
+          <t>33,11</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,01; 39,46</t>
+          <t>27,7; 39,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,8; 37,12</t>
+          <t>26,65; 37,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,12; 37,07</t>
+          <t>29,17; 37,93</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,67</t>
+          <t>40,51</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,14</t>
+          <t>35,1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,37</t>
+          <t>37,98</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 42,32</t>
+          <t>35,06; 48,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,81; 40,24</t>
+          <t>30,66; 39,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 39,03</t>
+          <t>34,19; 42,96</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>35,45</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,59</t>
+          <t>32,03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,16</t>
+          <t>34,14</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,36; 38,96</t>
+          <t>31,58; 39,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,85; 35,71</t>
+          <t>27,87; 38,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,05; 36,2</t>
+          <t>31,16; 37,58</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>38,26</t>
+          <t>37,67</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>32,67</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,55</t>
+          <t>35,46</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,87; 43,63</t>
+          <t>33,41; 43,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 34,43</t>
+          <t>28,62; 37,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 36,86</t>
+          <t>32,3; 39,1</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>40,63</t>
+          <t>40,81</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,76</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38,51</t>
+          <t>38,83</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,49; 46,01</t>
+          <t>35,98; 46,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,93; 41,6</t>
+          <t>33,57; 42,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,4; 41,71</t>
+          <t>35,67; 42,46</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>38,44</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>37,51</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>38,01</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,75; 39,01</t>
+          <t>36,09; 41,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 38,11</t>
+          <t>35,23; 40,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,07; 38,27</t>
+          <t>36,36; 39,82</t>
         </is>
       </c>
     </row>
